--- a/2nd_artifacts/astropy_12907/eval/ground_truth_astropy12907_iter3.xlsx
+++ b/2nd_artifacts/astropy_12907/eval/ground_truth_astropy12907_iter3.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="158">
   <si>
     <t xml:space="preserve">Ground truth answer key: astropy__astropy-12907 (iteration 3, rulings applied)</t>
   </si>
@@ -310,7 +310,7 @@
     <t xml:space="preserve">working nodes (Realizes GT-*):</t>
   </si>
   <si>
-    <t xml:space="preserve">Key findings: decisions that are John's (and Dr. Nasim's)</t>
+    <t xml:space="preserve">Key findings: decisions</t>
   </si>
   <si>
     <t xml:space="preserve">Each row is a judgment call the draft could not make. The last column records the ruling; rulings override every draft row in the other sheets.</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">Model tree has imperative-under-imperative chains (P5.1 under P5; P6.1 under P6), a shape prior trees never had.</t>
   </si>
   <si>
-    <t xml:space="preserve">Surface to Dr. Nasim; request does not forbid it; no GT change.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACCEPTED, RULED by Dr. Nasim, Jul 21. Imperatives are terminal. A definitive may
+    <t xml:space="preserve">request does not forbid it; no GT change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCEPTED, RULED, Jul 21. Imperatives are terminal. A definitive may
 bear multiple imperative children executed in sequence; sibling order is
 enforcement order, not lineage. Her test: each imperative must map to its
 own execution call, which P5 and P5.1 satisfy (enforcer = execute). The
@@ -384,10 +384,10 @@
     <t xml:space="preserve">Does the safety-first invariant (arbitrate) convention extend to repair-style intents? (GT row P8)</t>
   </si>
   <si>
-    <t xml:space="preserve">Keep for cross-GT uniformity, excluded from recall as always; strike if Dr. Nasim rules it enforcement-only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REMOVE (John's call, Jul 26, pending Dr. Nasim). The arbitrate node is
+    <t xml:space="preserve">Keep for cross-GT uniformity, excluded from recall as always;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMOVE  The arbitrate node is
 struck from the GT. Basis: the published protect_files GT (paper Table I
 and the protect_files workbook) contains no arbitrate node, so the
 safety-invariant convention is study-specific rather than universal. The
@@ -410,7 +410,7 @@
 Basis (b) field semantics: T is time only (always, deadlines, windows), so a condition-bounded value
 such as "once, until verified" is a firing condition and belongs to monitored state, not to the tuple,
 the same rule already applied to the embodied turn-off-before-wipe ordering.
-Consequence: with the root at always the intent is standing, which is Dr. Nasim's intent-management
+Consequence: with the root at always the intent is standing, which is ref paper intent-management
 default, so a continuous Monitor policy is derivable from the intent and M-P1 is relevant.
 Recall unaffected: the 6 enumerated obligations are each grounded in the issue text or benchmark
 artifacts and monitoring is grounded in neither; a standing repository watch belongs to the enclosing
@@ -428,7 +428,7 @@
     <t xml:space="preserve">Disclose wherever the tree is presented; specificity and coverage may be inflated; TC/AC/EF unaffected (structural).</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED. Dr. Nasim attributed _cstack to training recall ("because
+    <t xml:space="preserve">ACCEPTED.  _cstack to training recall ("because
 they've been trained, right?") and framed the test as relevance rather
 than scope. Disclosure stance unchanged: disclose whenever the tree is
 shown, note that content specificity may be inflated, TC/AC/EF are
@@ -450,7 +450,7 @@
     <t xml:space="preserve">REQ-V1 FROZEN for the scored pilot. The Q1 grammar line is a v2 change applied at the execution-arm
 stage, not retro-fitted. Editing v1 would desynchronize the scored trees from the request that produced
 them and break the FormatSpread (Sclar et al., ICLR 2024) rationale for freezing, up to 76 points of
-swing from formatting alone. No re-run is required: Dr. Nasim's Jul 21 ruling makes the existing tree
+swing from formatting alone. No re-run is required: Meeting on Jul 21 ruling makes the existing tree
 interpretable as it stands. Disclose the v1/v2 boundary when execution-arm results are reported.</t>
   </si>
   <si>
@@ -460,7 +460,7 @@
     <t xml:space="preserve">Field semantics already admit always, deadlines, and windows (time only). Conditions are firing conditions in monitored state, not T.</t>
   </si>
   <si>
-    <t xml:space="preserve">OPEN for Dr. Nasim (Q4). Not blocking. This GT uses always on every node, consistent with all prior GTs,
+    <t xml:space="preserve">Not blocking. This GT uses always on every node, consistent with all prior GTs,
 so scoring proceeds either way. The question for her is narrower than it looks: the tuple is not locked to
 always, since T admits deadlines and windows by definition. What needs her convention is whether a
 condition-bounded temporal ("until verified", "until the suite passes") is ever admissible in T, or whether
@@ -474,7 +474,7 @@
     <t xml:space="preserve">The tree covered Analyze, Plan and Execute but had no Monitor enforcer, in a MAPE-K framing.</t>
   </si>
   <si>
-    <t xml:space="preserve">ADDED, John's call, Jul 26. New scaffolding definitive P9 (Monitor / observe) under P0, and P4 reparented
+    <t xml:space="preserve">ADDED, Jul 26. New scaffolding definitive P9 (Monitor / observe) under P0, and P4 reparented
 from P1 to P9. Basis: confirming the defect is present in the current code before changing it is bounded
 baseline observation, grounded in the intent supplying three reproduction blocks as its own evidence. It is
 distinct from a standing watch for recurrence, which stays out of the answer key (Assumptions A3).
@@ -530,6 +530,22 @@
 schema present. The same drift appears in its structured tree (P4.2, P6, P7). The schema is
 therefore not the cause, which defuses the scope-creep reading of Key Findings #2 and #3.
 Gemini drifted far less in both cells, so the trait is model-dependent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting-2 divergence: is the pilot's plan_unstructured the same instrument as the paper's Setting 2?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No, and deliberately. Disclosed here so the difference is on record, not reconstructed later.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISCLOSED, Jul 26. Two differences from the paper's Setting 2, both deliberate. Persona: the paper
+used "you are an autonomous coding agent"; the pilot uses the frozen request's own persona sentence,
+held byte-identical with the structured request so representation is the single variable. Task
+wording: the paper's S2 was near-bare; the pilot keeps the word "policies" and the decompose-first
+instruction. Rationale: the vocabulary of the OBJECT stays, the vocabulary of the REPRESENTATION
+goes; asking both arms for policies and giving only one the schema is the harder baseline. Do not
+compare pilot plan_unstructured numbers against paper S2 numbers without naming both instruments;
+see vocabulary_map.md.</t>
   </si>
   <si>
     <t xml:space="preserve">Declared assumptions and scope, astropy__astropy-12907</t>
@@ -811,7 +827,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="52"/>
@@ -950,7 +966,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -1444,7 +1460,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="54.98"/>
@@ -1596,7 +1612,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="113" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>9</v>
       </c>
@@ -1610,7 +1626,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="124.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>10</v>
       </c>
@@ -1624,7 +1640,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="224.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>11</v>
       </c>
@@ -1666,8 +1682,19 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0"/>
+    <row r="18" customFormat="false" ht="90.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>141</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1690,21 +1717,21 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="118"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="118"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B2" s="7"/>
     </row>
@@ -1714,42 +1741,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1758,10 +1785,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1770,10 +1797,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/2nd_artifacts/astropy_12907/eval/ground_truth_astropy12907_iter3.xlsx
+++ b/2nd_artifacts/astropy_12907/eval/ground_truth_astropy12907_iter3.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Answer_key" sheetId="1" state="visible" r:id="rId2"/>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">Declared assumptions and scope, astropy__astropy-12907</t>
   </si>
   <si>
-    <t xml:space="preserve">These are the stated bases on which the scoring is performed. They are assumptions, not findings, and each is reversible on Dr. Nasim's ruling.</t>
+    <t xml:space="preserve">These are the stated bases on which the scoring is performed. They are assumptions, not findings, and each is reversible on author's ruling.</t>
   </si>
   <si>
     <t xml:space="preserve">A1. Intent temporality</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">The model tree names _cstack without repository access and the request contains no such string. This is training recall. Disclose wherever the tree is presented; content specificity may be inflated; TC/AC/EF are structural and untouched. See Key Findings #7.</t>
   </si>
   <si>
-    <t xml:space="preserve">Open for Dr. Nasim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3: does the safety-first arbitrate convention extend to repair intents (Key Findings #5, struck as John's call, score-neutral). Q4: may T carry a condition-bounded value, or must conditions be monitored state (Key Findings #10). Neither blocks scoring.</t>
+    <t xml:space="preserve">Open For Meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3: does the safety-first arbitrate convention extend to repair intents (Key Findings #5, struck as author's call, score-neutral). Q4: may T carry a condition-bounded value, or must conditions be monitored state (Key Findings #10). Neither blocks scoring.</t>
   </si>
   <si>
     <t xml:space="preserve">Design axis to record in Discussion, not a scoring input</t>
   </si>
   <si>
-    <t xml:space="preserve">Loop re-entry is an explicit design decision: periodic re-execution at a fixed interval versus change-triggered re-entry on a monitoring-data delta. Dr. Nasim raised it on Jul 21 and asked that it be named rather than assumed. Anchor: 'Some people see if there is any change in monitoring data'.</t>
+    <t xml:space="preserve">Loop re-entry is an explicit design decision: periodic re-execution at a fixed interval versus change-triggered re-entry on a monitoring-data delta. Co-author raised it on Jul 21 and asked that it be named rather than assumed. Anchor: 'Some people see if there is any change in monitoring data'.</t>
   </si>
 </sst>
 </file>
@@ -827,7 +827,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="52"/>
@@ -966,7 +966,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -1460,7 +1460,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="54.98"/>
@@ -1717,7 +1717,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="118"/>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B1" s="7"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>143</v>
       </c>
@@ -1783,7 +1783,7 @@
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
         <v>154</v>
       </c>
@@ -1795,7 +1795,7 @@
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
         <v>156</v>
       </c>
